--- a/sheet/MonsterCardData.xlsx
+++ b/sheet/MonsterCardData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspace\nanDeck\DungeonCrawlDeckMaster\sheet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDEF5B96-A0C8-4FBC-A856-D7F5D5DA3703}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{426E3936-0023-4598-A845-7CF738C46E3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -705,11 +705,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>回合结束时：移动1格，然后本牌点数减1。&lt;br&gt;
-本牌因点数为0而被消灭时：使同房间内所有其他牌点数减1。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>哨戒无人机</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -770,7 +765,12 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>回合结束时：如果本牌所在房间没有其他牌，将本牌移动1格。否则选同房间1张其他牌，使其点数减1，同房间对侧有牌时，只能选对侧的牌。</t>
+    <t>回合结束时：移动1格，然后本牌点数减1。&lt;br&gt;
+本牌因点数为0而被消灭时：使同房间内所有其他牌点数减1，然后玩家受到1伤害。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>回合结束时：如果本牌所在房间没有其他牌，将本牌移动1格。否则选同房间1张其他牌，使其点数减1。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1187,7 +1187,7 @@
         <v>4</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>7</v>
@@ -1235,7 +1235,7 @@
         <v>4</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>163</v>
+        <v>177</v>
       </c>
       <c r="F5" s="3" t="s">
         <v>141</v>
@@ -1247,7 +1247,7 @@
     </row>
     <row r="6" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B6" t="s">
         <v>122</v>
@@ -1259,10 +1259,10 @@
         <v>4</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>142</v>
@@ -1271,7 +1271,7 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B7" t="s">
         <v>122</v>
@@ -1283,10 +1283,10 @@
         <v>4</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G7" s="2"/>
       <c r="H7" s="3"/>
@@ -1425,7 +1425,7 @@
         <v>4</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F13" s="3" t="s">
         <v>140</v>
@@ -1449,7 +1449,7 @@
         <v>4</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>17</v>
@@ -1475,7 +1475,7 @@
         <v>4</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F15" s="3" t="s">
         <v>134</v>
@@ -1511,7 +1511,7 @@
     </row>
     <row r="17" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B17" t="s">
         <v>15</v>
@@ -1523,7 +1523,7 @@
         <v>4</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="F17" s="3" t="s">
         <v>136</v>
@@ -1924,7 +1924,7 @@
         <v>4</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="F33" s="3" t="s">
         <v>104</v>
@@ -2143,7 +2143,7 @@
         <v>4</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F42" s="3" t="s">
         <v>80</v>

--- a/sheet/MonsterCardData.xlsx
+++ b/sheet/MonsterCardData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspace\nanDeck\DungeonCrawlDeckMaster\sheet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{426E3936-0023-4598-A845-7CF738C46E3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64692346-BE1C-41D0-80D8-DB9EAC5B53FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4290" yWindow="3480" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -717,10 +717,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>回合结束时：如果同房间同侧没有其他怪物牌，则将主牌堆第1张怪物牌加入本牌所在房间同侧；否则移动1格。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Turret</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -734,10 +730,6 @@
   </si>
   <si>
     <t>死亡时：翻开主牌堆的“史莱姆牌”直到合计点数不小于本牌点数，然后选其中1张牌加入本牌所在房间同侧，其余的牌加入手牌。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>回合结束时：如果本牌点数为1，则本牌点数加1。否则本牌点数减1，然后将主牌堆第1张同名牌加入与本牌相邻的房间同侧。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -765,12 +757,21 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>回合结束时：移动1格，然后本牌点数减1。&lt;br&gt;
-本牌因点数为0而被消灭时：使同房间内所有其他牌点数减1，然后玩家受到1伤害。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>回合结束时：如果本牌所在房间没有其他牌，将本牌移动1格。否则选同房间1张其他牌，使其点数减1。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>回合结束时：移动1格。&lt;br&gt;
+移动时：点数减1。&lt;br&gt;
+点数为0而被消灭时：使同房间内所有其他牌点数减1，然后玩家受到1伤害。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>回合结束时：如果同房间同侧没有其他怪物牌，则将主牌堆第1张怪物牌加入本牌所在房间同侧，然后移动1格。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>回合结束时：将主牌堆第1张同名牌加入与本牌相邻的房间同侧。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1187,7 +1188,7 @@
         <v>4</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>7</v>
@@ -1221,7 +1222,7 @@
       </c>
       <c r="H4" s="3"/>
     </row>
-    <row r="5" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:9" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>123</v>
       </c>
@@ -1229,13 +1230,13 @@
         <v>122</v>
       </c>
       <c r="C5" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D5" s="2">
         <v>4</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F5" s="3" t="s">
         <v>141</v>
@@ -1259,7 +1260,7 @@
         <v>4</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>166</v>
+        <v>177</v>
       </c>
       <c r="F6" s="3" t="s">
         <v>164</v>
@@ -1283,10 +1284,10 @@
         <v>4</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G7" s="2"/>
       <c r="H7" s="3"/>
@@ -1425,7 +1426,7 @@
         <v>4</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F13" s="3" t="s">
         <v>140</v>
@@ -1449,7 +1450,7 @@
         <v>4</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>17</v>
@@ -1461,7 +1462,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>124</v>
       </c>
@@ -1475,7 +1476,7 @@
         <v>4</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="F15" s="3" t="s">
         <v>134</v>
@@ -1499,7 +1500,7 @@
         <v>4</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="F16" s="3" t="s">
         <v>135</v>
@@ -1511,7 +1512,7 @@
     </row>
     <row r="17" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B17" t="s">
         <v>15</v>
@@ -1523,7 +1524,7 @@
         <v>4</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="F17" s="3" t="s">
         <v>136</v>
@@ -1924,7 +1925,7 @@
         <v>4</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="F33" s="3" t="s">
         <v>104</v>
@@ -2143,7 +2144,7 @@
         <v>4</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="F42" s="3" t="s">
         <v>80</v>

--- a/sheet/MonsterCardData.xlsx
+++ b/sheet/MonsterCardData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspace\nanDeck\DungeonCrawlDeckMaster\sheet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64692346-BE1C-41D0-80D8-DB9EAC5B53FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0E6122E-55A5-419C-AF66-50DC204F1BEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4290" yWindow="3480" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5400" yWindow="3045" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -548,10 +548,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>软泥怪</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>送墓时：选弃牌堆1张怪物牌放在房间区任意位置或加入手牌。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -588,10 +584,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Sludge</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Metal slime</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -605,10 +597,6 @@
   </si>
   <si>
     <t>Mob slime</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Slime tower</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -701,10 +689,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>回合结束时：将本牌与同房间同侧至多1张牌一起移动1格。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>哨戒无人机</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -721,15 +705,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>回合结束时：如果同房间内有陷阱牌，则消灭同房间内所有陷阱牌；否则，将主牌堆或弃牌堆第1张陷阱牌加入本牌所在房间同侧，之后移动1格。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>回合结束时：选同行列其他房间对侧的1张怪物牌，使其点数减1。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>死亡时：翻开主牌堆的“史莱姆牌”直到合计点数不小于本牌点数，然后选其中1张牌加入本牌所在房间同侧，其余的牌加入手牌。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -742,11 +718,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>开战前：呼唤场上同侧所有“史莱姆”牌。&lt;br&gt;
-回合结束时：呼唤场上同侧另1张“史莱姆”牌。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>持续：同房间同侧所有怪物牌点数加1。&lt;br&gt;
 死亡时：本牌移动到一个同侧有怪物牌的相邻房间。</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -754,10 +725,6 @@
   <si>
     <t>回合结束时：玩家受到1伤害，然后弃置本牌。&lt;br&gt;
 开战前：呼唤弃牌堆所有同名牌。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>回合结束时：如果本牌所在房间没有其他牌，将本牌移动1格。否则选同房间1张其他牌，使其点数减1。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -767,11 +734,44 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>回合结束时：如果同房间同侧没有其他怪物牌，则将主牌堆第1张怪物牌加入本牌所在房间同侧，然后移动1格。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>回合结束时：将主牌堆第1张同名牌加入与本牌相邻的房间同侧。</t>
+    <t>飞溅史莱姆</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>死亡时：从主牌堆翻开1张同名牌放在相邻房间同侧。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Splash slime</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>点数下降时：将主牌堆第1张“史莱姆”牌加入手牌。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>回合结束时：移动1格。然后如果同房间内有陷阱牌，则消灭同房间内1张陷阱牌；否则，从主牌堆或弃牌堆呼唤第1张陷阱牌。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>回合结束时：将本牌与同房间至多1张其他牌一起移动1格。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>回合结束时：移动1格。然后如果同房间有敌对怪物牌，则呼唤主牌堆第1张怪物牌。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Slime tower</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>回合结束时：呼唤主牌堆第1张同名牌到与本牌相邻的房间。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>开战前：呼唤场上所有“史莱姆”牌。&lt;br&gt;
+回合结束时：呼唤场上另1张“史莱姆”牌。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1155,22 +1155,22 @@
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
+        <v>130</v>
+      </c>
+      <c r="B2" t="s">
         <v>131</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" s="1">
+        <v>1</v>
+      </c>
+      <c r="D2" s="2">
+        <v>4</v>
+      </c>
+      <c r="F2" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="C2" s="1">
-        <v>1</v>
-      </c>
-      <c r="D2" s="2">
-        <v>4</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>133</v>
-      </c>
       <c r="G2" s="2" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="H2" s="3"/>
     </row>
@@ -1188,19 +1188,19 @@
         <v>4</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>7</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="H3" s="3"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="B4" t="s">
         <v>122</v>
@@ -1212,13 +1212,13 @@
         <v>4</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>162</v>
+        <v>174</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="H4" s="3"/>
     </row>
@@ -1236,19 +1236,19 @@
         <v>4</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="H5" s="3"/>
     </row>
-    <row r="6" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="B6" t="s">
         <v>122</v>
@@ -1260,19 +1260,19 @@
         <v>4</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="H6" s="3"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="B7" t="s">
         <v>122</v>
@@ -1284,10 +1284,10 @@
         <v>4</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="G7" s="2"/>
       <c r="H7" s="3"/>
@@ -1318,7 +1318,7 @@
     </row>
     <row r="9" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="B9" t="s">
         <v>8</v>
@@ -1333,7 +1333,7 @@
         <v>115</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>9</v>
@@ -1378,7 +1378,7 @@
         <v>4</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="F11" s="3" t="s">
         <v>102</v>
@@ -1405,31 +1405,31 @@
       </c>
       <c r="E12" s="2"/>
       <c r="F12" s="3" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>16</v>
       </c>
       <c r="H12" s="4"/>
     </row>
-    <row r="13" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>120</v>
+        <v>169</v>
       </c>
       <c r="B13" t="s">
         <v>15</v>
       </c>
       <c r="C13" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D13" s="2">
         <v>4</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>140</v>
+        <v>171</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>16</v>
@@ -1450,7 +1450,7 @@
         <v>4</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>17</v>
@@ -1476,34 +1476,34 @@
         <v>4</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>16</v>
       </c>
       <c r="H15" s="4"/>
     </row>
-    <row r="16" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="B16" t="s">
         <v>15</v>
       </c>
       <c r="C16" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D16" s="2">
         <v>4</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>135</v>
+        <v>176</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>16</v>
@@ -1512,7 +1512,7 @@
     </row>
     <row r="17" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="B17" t="s">
         <v>15</v>
@@ -1524,10 +1524,10 @@
         <v>4</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>16</v>
@@ -1548,7 +1548,7 @@
         <v>4</v>
       </c>
       <c r="E18" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="F18" s="3" t="s">
         <v>4</v>
@@ -1574,7 +1574,7 @@
         <v>4</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="F19" s="3" t="s">
         <v>21</v>
@@ -1641,7 +1641,7 @@
         <v>27</v>
       </c>
       <c r="B22" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="C22" s="1">
         <v>1</v>
@@ -1650,7 +1650,7 @@
         <v>4</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="F22" s="3" t="s">
         <v>29</v>
@@ -1665,16 +1665,16 @@
         <v>30</v>
       </c>
       <c r="B23" t="s">
+        <v>144</v>
+      </c>
+      <c r="C23" s="1">
+        <v>1</v>
+      </c>
+      <c r="D23" s="2">
+        <v>4</v>
+      </c>
+      <c r="E23" s="2" t="s">
         <v>147</v>
-      </c>
-      <c r="C23" s="1">
-        <v>1</v>
-      </c>
-      <c r="D23" s="2">
-        <v>4</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>150</v>
       </c>
       <c r="F23" s="3" t="s">
         <v>31</v>
@@ -1688,10 +1688,10 @@
     </row>
     <row r="24" spans="1:9" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="B24" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="C24" s="1">
         <v>2</v>
@@ -1700,7 +1700,7 @@
         <v>4</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="F24" s="3" t="s">
         <v>33</v>
@@ -1715,7 +1715,7 @@
         <v>34</v>
       </c>
       <c r="B25" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="C25" s="1">
         <v>2</v>
@@ -1741,7 +1741,7 @@
         <v>0</v>
       </c>
       <c r="B26" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="C26" s="1">
         <v>1</v>
@@ -1777,7 +1777,7 @@
         <v>4</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="F27" s="3" t="s">
         <v>40</v>
@@ -1803,7 +1803,7 @@
         <v>4</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="F28" s="3" t="s">
         <v>43</v>
@@ -1827,7 +1827,7 @@
         <v>4</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="F29" s="3" t="s">
         <v>47</v>
@@ -1841,10 +1841,10 @@
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
+        <v>128</v>
+      </c>
+      <c r="B30" t="s">
         <v>129</v>
-      </c>
-      <c r="B30" t="s">
-        <v>130</v>
       </c>
       <c r="C30" s="1">
         <v>1</v>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="E30" s="2"/>
       <c r="F30" s="3" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>51</v>
@@ -1875,7 +1875,7 @@
         <v>4</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F31" s="3" t="s">
         <v>52</v>
@@ -1901,7 +1901,7 @@
         <v>4</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F32" s="3" t="s">
         <v>107</v>
@@ -1925,7 +1925,7 @@
         <v>4</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="F33" s="3" t="s">
         <v>104</v>
@@ -1939,7 +1939,7 @@
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B34" t="s">
         <v>50</v>
@@ -1951,10 +1951,10 @@
         <v>4</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="G34" s="2" t="s">
         <v>51</v>
@@ -1975,7 +1975,7 @@
         <v>4</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="F35" s="3" t="s">
         <v>60</v>
@@ -2001,7 +2001,7 @@
         <v>4</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="F36" s="3" t="s">
         <v>108</v>
@@ -2144,7 +2144,7 @@
         <v>4</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="F42" s="3" t="s">
         <v>80</v>

--- a/sheet/MonsterCardData.xlsx
+++ b/sheet/MonsterCardData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspace\nanDeck\DungeonCrawlDeckMaster\sheet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0E6122E-55A5-419C-AF66-50DC204F1BEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50840CFE-A5E1-438F-85FC-B6EC16A44D6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5400" yWindow="3045" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -705,10 +705,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>回合结束时：选同行列其他房间对侧的1张怪物牌，使其点数减1。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>交锋前：弃置本牌。&lt;br&gt;
 送墓时：玩家获得3金币。</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -772,6 +768,10 @@
   <si>
     <t>开战前：呼唤场上所有“史莱姆”牌。&lt;br&gt;
 回合结束时：呼唤场上另1张“史莱姆”牌。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>回合结束时：选同行列其他房间1张敌对怪物牌，使其点数减1。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1188,7 +1188,7 @@
         <v>4</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>7</v>
@@ -1212,7 +1212,7 @@
         <v>4</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F4" s="3" t="s">
         <v>158</v>
@@ -1236,7 +1236,7 @@
         <v>4</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="F5" s="3" t="s">
         <v>138</v>
@@ -1260,7 +1260,7 @@
         <v>4</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F6" s="3" t="s">
         <v>160</v>
@@ -1284,7 +1284,7 @@
         <v>4</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>163</v>
+        <v>178</v>
       </c>
       <c r="F7" s="3" t="s">
         <v>162</v>
@@ -1414,7 +1414,7 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B13" t="s">
         <v>15</v>
@@ -1426,10 +1426,10 @@
         <v>4</v>
       </c>
       <c r="E13" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="F13" s="3" t="s">
         <v>170</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>171</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>16</v>
@@ -1450,7 +1450,7 @@
         <v>4</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>17</v>
@@ -1476,7 +1476,7 @@
         <v>4</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F15" s="3" t="s">
         <v>133</v>
@@ -1500,10 +1500,10 @@
         <v>4</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>16</v>
@@ -1512,7 +1512,7 @@
     </row>
     <row r="17" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B17" t="s">
         <v>15</v>
@@ -1524,7 +1524,7 @@
         <v>4</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="F17" s="3" t="s">
         <v>134</v>
@@ -1925,7 +1925,7 @@
         <v>4</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F33" s="3" t="s">
         <v>104</v>
@@ -2144,7 +2144,7 @@
         <v>4</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="F42" s="3" t="s">
         <v>80</v>

--- a/sheet/MonsterCardData.xlsx
+++ b/sheet/MonsterCardData.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspace\nanDeck\DungeonCrawlDeckMaster\sheet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50840CFE-A5E1-438F-85FC-B6EC16A44D6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E200CFC-B1CD-4A42-907A-A5B10A122C28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5400" yWindow="3045" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -746,14 +746,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>回合结束时：移动1格。然后如果同房间内有陷阱牌，则消灭同房间内1张陷阱牌；否则，从主牌堆或弃牌堆呼唤第1张陷阱牌。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>回合结束时：将本牌与同房间至多1张其他牌一起移动1格。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>回合结束时：移动1格。然后如果同房间有敌对怪物牌，则呼唤主牌堆第1张怪物牌。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -772,6 +764,15 @@
   </si>
   <si>
     <t>回合结束时：选同行列其他房间1张敌对怪物牌，使其点数减1。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>回合开始时：将本牌与同房间至多1张其他牌一起移动1格。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>回合开始时：移动1格。&lt;br&gt;
+回合结束时：如果同房间内有陷阱牌，则消灭同房间内1张陷阱牌；否则，从主牌堆或弃牌堆呼唤第1张陷阱牌。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1174,7 +1175,7 @@
       </c>
       <c r="H2" s="3"/>
     </row>
-    <row r="3" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:9" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -1188,7 +1189,7 @@
         <v>4</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>7</v>
@@ -1212,7 +1213,7 @@
         <v>4</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="F4" s="3" t="s">
         <v>158</v>
@@ -1260,7 +1261,7 @@
         <v>4</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="F6" s="3" t="s">
         <v>160</v>
@@ -1284,7 +1285,7 @@
         <v>4</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="F7" s="3" t="s">
         <v>162</v>
@@ -1450,7 +1451,7 @@
         <v>4</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>17</v>
@@ -1476,7 +1477,7 @@
         <v>4</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="F15" s="3" t="s">
         <v>133</v>
@@ -1503,7 +1504,7 @@
         <v>171</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>16</v>

--- a/sheet/MonsterCardData.xlsx
+++ b/sheet/MonsterCardData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspace\nanDeck\DungeonCrawlDeckMaster\sheet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E200CFC-B1CD-4A42-907A-A5B10A122C28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C65E7D0-ACF2-40AB-9B10-EA425E591F56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5400" yWindow="3045" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -724,55 +724,56 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>回合结束时：移动1格。&lt;br&gt;
+    <t>飞溅史莱姆</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>死亡时：从主牌堆翻开1张同名牌放在相邻房间同侧。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Splash slime</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>点数下降时：将主牌堆第1张“史莱姆”牌加入手牌。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Slime tower</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>回合结束时：呼唤主牌堆第1张同名牌到与本牌相邻的房间。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>开战前：呼唤场上所有“史莱姆”牌。&lt;br&gt;
+回合结束时：呼唤场上另1张“史莱姆”牌。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>回合结束时：选同行列其他房间1张敌对怪物牌，使其点数减1。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>回合开始时：将本牌与同房间至多1张其他牌一起移动1格。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>回合开始时：移动1格。&lt;br&gt;
+回合结束时：如果同房间内有陷阱牌，则消灭同房间内1张陷阱牌；否则，从主牌堆或弃牌堆呼唤第1张陷阱牌。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>回合开始时：移动1格。&lt;br&gt;
 移动时：点数减1。&lt;br&gt;
 点数为0而被消灭时：使同房间内所有其他牌点数减1，然后玩家受到1伤害。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>飞溅史莱姆</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>死亡时：从主牌堆翻开1张同名牌放在相邻房间同侧。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Splash slime</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>点数下降时：将主牌堆第1张“史莱姆”牌加入手牌。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>回合结束时：移动1格。然后如果同房间有敌对怪物牌，则呼唤主牌堆第1张怪物牌。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Slime tower</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>回合结束时：呼唤主牌堆第1张同名牌到与本牌相邻的房间。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>开战前：呼唤场上所有“史莱姆”牌。&lt;br&gt;
-回合结束时：呼唤场上另1张“史莱姆”牌。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>回合结束时：选同行列其他房间1张敌对怪物牌，使其点数减1。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>回合开始时：将本牌与同房间至多1张其他牌一起移动1格。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>回合开始时：移动1格。&lt;br&gt;
-回合结束时：如果同房间内有陷阱牌，则消灭同房间内1张陷阱牌；否则，从主牌堆或弃牌堆呼唤第1张陷阱牌。</t>
+回合结束时：如果同房间有敌对怪物牌，则呼唤主牌堆第1张怪物牌。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1189,7 +1190,7 @@
         <v>4</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>7</v>
@@ -1213,7 +1214,7 @@
         <v>4</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="F4" s="3" t="s">
         <v>158</v>
@@ -1231,13 +1232,13 @@
         <v>122</v>
       </c>
       <c r="C5" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D5" s="2">
         <v>4</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>167</v>
+        <v>177</v>
       </c>
       <c r="F5" s="3" t="s">
         <v>138</v>
@@ -1247,7 +1248,7 @@
       </c>
       <c r="H5" s="3"/>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>159</v>
       </c>
@@ -1261,7 +1262,7 @@
         <v>4</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="F6" s="3" t="s">
         <v>160</v>
@@ -1285,7 +1286,7 @@
         <v>4</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="F7" s="3" t="s">
         <v>162</v>
@@ -1415,7 +1416,7 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B13" t="s">
         <v>15</v>
@@ -1427,10 +1428,10 @@
         <v>4</v>
       </c>
       <c r="E13" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="F13" s="3" t="s">
         <v>169</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>170</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>16</v>
@@ -1451,7 +1452,7 @@
         <v>4</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>17</v>
@@ -1477,7 +1478,7 @@
         <v>4</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="F15" s="3" t="s">
         <v>133</v>
@@ -1501,10 +1502,10 @@
         <v>4</v>
       </c>
       <c r="E16" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="F16" s="3" t="s">
         <v>171</v>
-      </c>
-      <c r="F16" s="3" t="s">
-        <v>173</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>16</v>

--- a/sheet/MonsterCardData.xlsx
+++ b/sheet/MonsterCardData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspace\nanDeck\DungeonCrawlDeckMaster\sheet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C65E7D0-ACF2-40AB-9B10-EA425E591F56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20CCF2ED-8348-41C1-9B49-13FF7F192CBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5400" yWindow="3045" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6090" yWindow="3735" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="179">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="185">
   <si>
     <t>掉宝地精</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -714,21 +714,12 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>持续：同房间同侧所有怪物牌点数加1。&lt;br&gt;
-死亡时：本牌移动到一个同侧有怪物牌的相邻房间。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>回合结束时：玩家受到1伤害，然后弃置本牌。&lt;br&gt;
 开战前：呼唤弃牌堆所有同名牌。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>飞溅史莱姆</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>死亡时：从主牌堆翻开1张同名牌放在相邻房间同侧。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -774,6 +765,39 @@
   <si>
     <t>回合开始时：移动1格。&lt;br&gt;
 回合结束时：如果同房间有敌对怪物牌，则呼唤主牌堆第1张怪物牌。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>死亡时：呼唤1张同名牌到相邻房间。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>持续：同房间所有友方怪物牌点数加1。&lt;br&gt;
+死亡时：移动到一个有友方怪物牌的相邻房间并免死。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>枪手</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>持续：本牌可以代替化身牌使用“弹药”牌。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>？</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>从手牌发动：替换场上1张点数小于本牌的牌。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>？？</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>送墓时：玩家抽1张牌。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1120,7 +1144,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I43"/>
+  <dimension ref="A1:I46"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="5" max="5" width="71" customWidth="1"/>
@@ -1190,7 +1214,7 @@
         <v>4</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>7</v>
@@ -1214,7 +1238,7 @@
         <v>4</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="F4" s="3" t="s">
         <v>158</v>
@@ -1238,7 +1262,7 @@
         <v>4</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="F5" s="3" t="s">
         <v>138</v>
@@ -1262,7 +1286,7 @@
         <v>4</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="F6" s="3" t="s">
         <v>160</v>
@@ -1286,7 +1310,7 @@
         <v>4</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="F7" s="3" t="s">
         <v>162</v>
@@ -1416,7 +1440,7 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B13" t="s">
         <v>15</v>
@@ -1428,10 +1452,10 @@
         <v>4</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>16</v>
@@ -1452,7 +1476,7 @@
         <v>4</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>17</v>
@@ -1478,7 +1502,7 @@
         <v>4</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="F15" s="3" t="s">
         <v>133</v>
@@ -1502,10 +1526,10 @@
         <v>4</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>16</v>
@@ -1588,159 +1612,143 @@
         <v>22</v>
       </c>
     </row>
-    <row r="20" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>91</v>
+        <v>179</v>
       </c>
       <c r="B20" t="s">
+        <v>20</v>
+      </c>
+      <c r="C20" s="1">
+        <v>1</v>
+      </c>
+      <c r="D20" s="2">
+        <v>4</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="F20" s="3"/>
+      <c r="G20" s="2"/>
+      <c r="H20" s="4"/>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>181</v>
+      </c>
+      <c r="B21" t="s">
         <v>92</v>
       </c>
-      <c r="C20" s="1">
-        <v>2</v>
-      </c>
-      <c r="D20" s="2">
-        <v>4</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A21" t="s">
-        <v>26</v>
-      </c>
-      <c r="B21" t="s">
+      <c r="C21" s="1">
+        <v>3</v>
+      </c>
+      <c r="D21" s="2">
+        <v>4</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="F21" s="3"/>
+      <c r="G21" s="2"/>
+      <c r="H21" s="4"/>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>183</v>
+      </c>
+      <c r="B22" t="s">
         <v>20</v>
       </c>
-      <c r="C21" s="1">
-        <v>1</v>
-      </c>
-      <c r="D21" s="2">
-        <v>4</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="H21" s="3"/>
-    </row>
-    <row r="22" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A22" t="s">
-        <v>27</v>
-      </c>
-      <c r="B22" t="s">
-        <v>145</v>
-      </c>
       <c r="C22" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D22" s="2">
         <v>4</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="H22" s="3"/>
+        <v>184</v>
+      </c>
+      <c r="F22" s="3"/>
+      <c r="G22" s="2"/>
+      <c r="H22" s="4"/>
     </row>
     <row r="23" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>30</v>
+        <v>91</v>
       </c>
       <c r="B23" t="s">
-        <v>144</v>
+        <v>92</v>
       </c>
       <c r="C23" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D23" s="2">
         <v>4</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>147</v>
+        <v>114</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" ht="42.75" x14ac:dyDescent="0.2">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>149</v>
+        <v>26</v>
       </c>
       <c r="B24" t="s">
-        <v>144</v>
+        <v>20</v>
       </c>
       <c r="C24" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D24" s="2">
         <v>4</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>148</v>
+        <v>121</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>33</v>
+        <v>103</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="H24" s="3"/>
     </row>
-    <row r="25" spans="1:9" ht="409.5" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="B25" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C25" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D25" s="2">
         <v>4</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>111</v>
+        <v>146</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="H25" s="4" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" ht="142.5" x14ac:dyDescent="0.2">
+      <c r="H25" s="3"/>
+    </row>
+    <row r="26" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="B26" t="s">
         <v>144</v>
@@ -1752,149 +1760,151 @@
         <v>4</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>113</v>
+        <v>147</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="H26" s="4" t="s">
+      <c r="H26" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
+        <v>149</v>
+      </c>
+      <c r="B27" t="s">
+        <v>144</v>
+      </c>
+      <c r="C27" s="1">
         <v>2</v>
       </c>
-      <c r="I26" s="4"/>
-    </row>
-    <row r="27" spans="1:9" ht="384.75" x14ac:dyDescent="0.2">
-      <c r="A27" t="s">
+      <c r="D27" s="2">
+        <v>4</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H27" s="3"/>
+    </row>
+    <row r="28" spans="1:9" ht="409.5" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
+        <v>34</v>
+      </c>
+      <c r="B28" t="s">
+        <v>144</v>
+      </c>
+      <c r="C28" s="1">
+        <v>2</v>
+      </c>
+      <c r="D28" s="2">
+        <v>4</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H28" s="4" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" ht="142.5" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
+        <v>0</v>
+      </c>
+      <c r="B29" t="s">
+        <v>144</v>
+      </c>
+      <c r="C29" s="1">
+        <v>1</v>
+      </c>
+      <c r="D29" s="2">
+        <v>4</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H29" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="I29" s="4"/>
+    </row>
+    <row r="30" spans="1:9" ht="384.75" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
         <v>37</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B30" t="s">
         <v>38</v>
       </c>
-      <c r="C27" s="1">
-        <v>1</v>
-      </c>
-      <c r="D27" s="2">
-        <v>4</v>
-      </c>
-      <c r="E27" s="2" t="s">
+      <c r="C30" s="1">
+        <v>1</v>
+      </c>
+      <c r="D30" s="2">
+        <v>4</v>
+      </c>
+      <c r="E30" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="F27" s="3" t="s">
+      <c r="F30" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="G27" s="2" t="s">
+      <c r="G30" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="H27" s="4" t="s">
+      <c r="H30" s="4" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="28" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A28" t="s">
+    <row r="31" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
         <v>42</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B31" t="s">
         <v>38</v>
       </c>
-      <c r="C28" s="1">
-        <v>1</v>
-      </c>
-      <c r="D28" s="2">
-        <v>4</v>
-      </c>
-      <c r="E28" s="2" t="s">
+      <c r="C31" s="1">
+        <v>1</v>
+      </c>
+      <c r="D31" s="2">
+        <v>4</v>
+      </c>
+      <c r="E31" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="F28" s="3" t="s">
+      <c r="F31" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="G28" s="2" t="s">
+      <c r="G31" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="H28" s="4"/>
-    </row>
-    <row r="29" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A29" t="s">
-        <v>44</v>
-      </c>
-      <c r="B29" t="s">
-        <v>45</v>
-      </c>
-      <c r="C29" s="1">
-        <v>1</v>
-      </c>
-      <c r="D29" s="2">
-        <v>4</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="G29" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="H29" s="3" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A30" t="s">
-        <v>128</v>
-      </c>
-      <c r="B30" t="s">
-        <v>129</v>
-      </c>
-      <c r="C30" s="1">
-        <v>1</v>
-      </c>
-      <c r="D30" s="2">
-        <v>4</v>
-      </c>
-      <c r="E30" s="2"/>
-      <c r="F30" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="G30" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="H30" s="3"/>
-    </row>
-    <row r="31" spans="1:9" ht="409.5" x14ac:dyDescent="0.2">
-      <c r="A31" t="s">
-        <v>49</v>
-      </c>
-      <c r="B31" t="s">
-        <v>50</v>
-      </c>
-      <c r="C31" s="1">
-        <v>1</v>
-      </c>
-      <c r="D31" s="2">
-        <v>4</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="F31" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="G31" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="H31" s="4" t="s">
-        <v>53</v>
-      </c>
+      <c r="H31" s="4"/>
     </row>
     <row r="32" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="B32" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="C32" s="1">
         <v>1</v>
@@ -1903,22 +1913,24 @@
         <v>4</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>127</v>
+        <v>150</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>107</v>
+        <v>47</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="H32" s="4"/>
-    </row>
-    <row r="33" spans="1:8" ht="409.5" x14ac:dyDescent="0.2">
+        <v>46</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>55</v>
+        <v>128</v>
       </c>
       <c r="B33" t="s">
-        <v>50</v>
+        <v>129</v>
       </c>
       <c r="C33" s="1">
         <v>1</v>
@@ -1926,22 +1938,18 @@
       <c r="D33" s="2">
         <v>4</v>
       </c>
-      <c r="E33" s="2" t="s">
-        <v>165</v>
-      </c>
+      <c r="E33" s="2"/>
       <c r="F33" s="3" t="s">
-        <v>104</v>
+        <v>135</v>
       </c>
       <c r="G33" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="H33" s="4" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="H33" s="3"/>
+    </row>
+    <row r="34" spans="1:8" ht="409.5" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>126</v>
+        <v>49</v>
       </c>
       <c r="B34" t="s">
         <v>50</v>
@@ -1953,93 +1961,95 @@
         <v>4</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>154</v>
+        <v>125</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>136</v>
+        <v>52</v>
       </c>
       <c r="G34" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="H34" s="4"/>
-    </row>
-    <row r="35" spans="1:8" ht="156.75" x14ac:dyDescent="0.2">
+      <c r="H34" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
+        <v>54</v>
+      </c>
+      <c r="B35" t="s">
+        <v>50</v>
+      </c>
+      <c r="C35" s="1">
+        <v>1</v>
+      </c>
+      <c r="D35" s="2">
+        <v>4</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="G35" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="H35" s="4"/>
+    </row>
+    <row r="36" spans="1:8" ht="409.5" x14ac:dyDescent="0.2">
+      <c r="A36" t="s">
+        <v>55</v>
+      </c>
+      <c r="B36" t="s">
+        <v>50</v>
+      </c>
+      <c r="C36" s="1">
+        <v>1</v>
+      </c>
+      <c r="D36" s="2">
+        <v>4</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="F36" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="G36" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="H36" s="4" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A37" t="s">
+        <v>126</v>
+      </c>
+      <c r="B37" t="s">
+        <v>50</v>
+      </c>
+      <c r="C37" s="1">
+        <v>1</v>
+      </c>
+      <c r="D37" s="2">
+        <v>4</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="F37" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="G37" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="H37" s="4"/>
+    </row>
+    <row r="38" spans="1:8" ht="156.75" x14ac:dyDescent="0.2">
+      <c r="A38" t="s">
         <v>57</v>
-      </c>
-      <c r="B35" t="s">
-        <v>58</v>
-      </c>
-      <c r="C35" s="1">
-        <v>1</v>
-      </c>
-      <c r="D35" s="2">
-        <v>4</v>
-      </c>
-      <c r="E35" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="F35" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="G35" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="H35" s="4" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A36" t="s">
-        <v>62</v>
-      </c>
-      <c r="B36" t="s">
-        <v>58</v>
-      </c>
-      <c r="C36" s="1">
-        <v>1</v>
-      </c>
-      <c r="D36" s="2">
-        <v>4</v>
-      </c>
-      <c r="E36" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="F36" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="G36" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="H36" s="4"/>
-    </row>
-    <row r="37" spans="1:8" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A37" t="s">
-        <v>94</v>
-      </c>
-      <c r="B37" t="s">
-        <v>63</v>
-      </c>
-      <c r="C37" s="1">
-        <v>1</v>
-      </c>
-      <c r="D37" s="2">
-        <v>4</v>
-      </c>
-      <c r="E37" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="F37" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="G37" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="H37" s="4"/>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A38" t="s">
-        <v>65</v>
       </c>
       <c r="B38" t="s">
         <v>58</v>
@@ -2051,136 +2061,210 @@
         <v>4</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>97</v>
+        <v>140</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>106</v>
+        <v>60</v>
       </c>
       <c r="G38" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="H38" s="4"/>
-    </row>
-    <row r="39" spans="1:8" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="H38" s="4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
+        <v>62</v>
+      </c>
+      <c r="B39" t="s">
+        <v>58</v>
+      </c>
+      <c r="C39" s="1">
+        <v>1</v>
+      </c>
+      <c r="D39" s="2">
+        <v>4</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="F39" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="G39" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="H39" s="4"/>
+    </row>
+    <row r="40" spans="1:8" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A40" t="s">
+        <v>94</v>
+      </c>
+      <c r="B40" t="s">
+        <v>63</v>
+      </c>
+      <c r="C40" s="1">
+        <v>1</v>
+      </c>
+      <c r="D40" s="2">
+        <v>4</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="F40" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="G40" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="H40" s="4"/>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A41" t="s">
+        <v>65</v>
+      </c>
+      <c r="B41" t="s">
+        <v>58</v>
+      </c>
+      <c r="C41" s="1">
+        <v>1</v>
+      </c>
+      <c r="D41" s="2">
+        <v>4</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="F41" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="G41" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="H41" s="4"/>
+    </row>
+    <row r="42" spans="1:8" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A42" t="s">
         <v>66</v>
       </c>
-      <c r="B39" t="s">
+      <c r="B42" t="s">
         <v>67</v>
       </c>
-      <c r="C39" s="1">
+      <c r="C42" s="1">
         <v>2</v>
       </c>
-      <c r="D39" s="2">
-        <v>4</v>
-      </c>
-      <c r="E39" s="2" t="s">
+      <c r="D42" s="2">
+        <v>4</v>
+      </c>
+      <c r="E42" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="F39" s="3" t="s">
+      <c r="F42" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="G39" s="2" t="s">
+      <c r="G42" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="H39" s="4"/>
-    </row>
-    <row r="40" spans="1:8" ht="42.75" x14ac:dyDescent="0.2">
-      <c r="A40" t="s">
+      <c r="H42" s="4"/>
+    </row>
+    <row r="43" spans="1:8" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="A43" t="s">
         <v>70</v>
       </c>
-      <c r="B40" t="s">
+      <c r="B43" t="s">
         <v>71</v>
       </c>
-      <c r="C40" s="1">
-        <v>1</v>
-      </c>
-      <c r="D40" s="2">
-        <v>4</v>
-      </c>
-      <c r="E40" s="2" t="s">
+      <c r="C43" s="1">
+        <v>1</v>
+      </c>
+      <c r="D43" s="2">
+        <v>4</v>
+      </c>
+      <c r="E43" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="F40" s="3" t="s">
+      <c r="F43" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="G40" s="2" t="s">
+      <c r="G43" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="H40" s="4"/>
-    </row>
-    <row r="41" spans="1:8" ht="57" x14ac:dyDescent="0.2">
-      <c r="A41" t="s">
+      <c r="H43" s="4"/>
+    </row>
+    <row r="44" spans="1:8" ht="57" x14ac:dyDescent="0.2">
+      <c r="A44" t="s">
         <v>73</v>
       </c>
-      <c r="B41" t="s">
+      <c r="B44" t="s">
         <v>74</v>
       </c>
-      <c r="C41" s="1">
-        <v>1</v>
-      </c>
-      <c r="D41" s="2">
-        <v>4</v>
-      </c>
-      <c r="E41" s="2" t="s">
+      <c r="C44" s="1">
+        <v>1</v>
+      </c>
+      <c r="D44" s="2">
+        <v>4</v>
+      </c>
+      <c r="E44" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="F41" s="3" t="s">
+      <c r="F44" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="G41" s="2" t="s">
+      <c r="G44" s="2" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="42" spans="1:8" ht="142.5" x14ac:dyDescent="0.2">
-      <c r="A42" t="s">
+    <row r="45" spans="1:8" ht="142.5" x14ac:dyDescent="0.2">
+      <c r="A45" t="s">
         <v>77</v>
       </c>
-      <c r="B42" t="s">
+      <c r="B45" t="s">
         <v>78</v>
       </c>
-      <c r="C42" s="1">
-        <v>1</v>
-      </c>
-      <c r="D42" s="2">
-        <v>4</v>
-      </c>
-      <c r="E42" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="F42" s="3" t="s">
+      <c r="C45" s="1">
+        <v>1</v>
+      </c>
+      <c r="D45" s="2">
+        <v>4</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="F45" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="G42" s="2" t="s">
+      <c r="G45" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="H42" s="4" t="s">
+      <c r="H45" s="4" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A43" t="s">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A46" t="s">
         <v>93</v>
       </c>
-      <c r="B43" t="s">
+      <c r="B46" t="s">
         <v>74</v>
       </c>
-      <c r="C43" s="1">
-        <v>1</v>
-      </c>
-      <c r="D43" s="2">
-        <v>4</v>
-      </c>
-      <c r="E43" s="2" t="s">
+      <c r="C46" s="1">
+        <v>1</v>
+      </c>
+      <c r="D46" s="2">
+        <v>4</v>
+      </c>
+      <c r="E46" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="F43" s="3" t="s">
+      <c r="F46" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="G43" s="2" t="s">
+      <c r="G46" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="H43" s="3"/>
+      <c r="H46" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/sheet/MonsterCardData.xlsx
+++ b/sheet/MonsterCardData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspace\nanDeck\DungeonCrawlDeckMaster\sheet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20CCF2ED-8348-41C1-9B49-13FF7F192CBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03C42B0A-A623-4410-A0CA-846D9880640C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6090" yWindow="3735" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -735,25 +735,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>回合结束时：呼唤主牌堆第1张同名牌到与本牌相邻的房间。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>开战前：呼唤场上所有“史莱姆”牌。&lt;br&gt;
-回合结束时：呼唤场上另1张“史莱姆”牌。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>回合结束时：选同行列其他房间1张敌对怪物牌，使其点数减1。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>回合开始时：将本牌与同房间至多1张其他牌一起移动1格。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>回合开始时：移动1格。&lt;br&gt;
-回合结束时：如果同房间内有陷阱牌，则消灭同房间内1张陷阱牌；否则，从主牌堆或弃牌堆呼唤第1张陷阱牌。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -763,15 +745,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>回合开始时：移动1格。&lt;br&gt;
-回合结束时：如果同房间有敌对怪物牌，则呼唤主牌堆第1张怪物牌。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>死亡时：呼唤1张同名牌到相邻房间。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>持续：同房间所有友方怪物牌点数加1。&lt;br&gt;
 死亡时：移动到一个有友方怪物牌的相邻房间并免死。</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -798,6 +771,33 @@
   </si>
   <si>
     <t>送墓时：玩家抽1张牌。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>回合开始时：移动1格。&lt;br&gt;
+回合结束时：如果同房间内有陷阱牌，则消灭同房间内1张陷阱牌。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>回合开始时：移动1格。&lt;br&gt;
+回合结束时：如果同房间有敌对怪物牌，则召集相邻房间1张友方怪物牌。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>回合结束时：选同行列中1张点数与本牌一致的怪物牌，使其点数减1。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>开战前：召集所有相邻房间的所有“史莱姆”牌。&lt;br&gt;
+回合结束时：召集相邻房间的1张“史莱姆”牌。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>回合结束时：召集主牌堆第1张同名牌到与本牌相邻的房间。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>死亡时：召集1张同名牌到相邻房间。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1200,7 +1200,7 @@
       </c>
       <c r="H2" s="3"/>
     </row>
-    <row r="3" spans="1:9" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -1214,7 +1214,7 @@
         <v>4</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>7</v>
@@ -1238,7 +1238,7 @@
         <v>4</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="F4" s="3" t="s">
         <v>158</v>
@@ -1262,7 +1262,7 @@
         <v>4</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="F5" s="3" t="s">
         <v>138</v>
@@ -1286,7 +1286,7 @@
         <v>4</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="F6" s="3" t="s">
         <v>160</v>
@@ -1310,7 +1310,7 @@
         <v>4</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>172</v>
+        <v>181</v>
       </c>
       <c r="F7" s="3" t="s">
         <v>162</v>
@@ -1452,7 +1452,7 @@
         <v>4</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="F13" s="3" t="s">
         <v>167</v>
@@ -1476,7 +1476,7 @@
         <v>4</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>171</v>
+        <v>182</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>17</v>
@@ -1502,7 +1502,7 @@
         <v>4</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>170</v>
+        <v>183</v>
       </c>
       <c r="F15" s="3" t="s">
         <v>133</v>
@@ -1614,7 +1614,7 @@
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="B20" t="s">
         <v>20</v>
@@ -1626,7 +1626,7 @@
         <v>4</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="F20" s="3"/>
       <c r="G20" s="2"/>
@@ -1634,7 +1634,7 @@
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="B21" t="s">
         <v>92</v>
@@ -1646,7 +1646,7 @@
         <v>4</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="F21" s="3"/>
       <c r="G21" s="2"/>
@@ -1654,7 +1654,7 @@
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="B22" t="s">
         <v>20</v>
@@ -1666,7 +1666,7 @@
         <v>4</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="F22" s="3"/>
       <c r="G22" s="2"/>
@@ -2011,7 +2011,7 @@
         <v>4</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="F36" s="3" t="s">
         <v>104</v>

--- a/sheet/MonsterCardData.xlsx
+++ b/sheet/MonsterCardData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspace\nanDeck\DungeonCrawlDeckMaster\sheet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03C42B0A-A623-4410-A0CA-846D9880640C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFA8FCF8-7E4D-4645-8AFE-3110695F51BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -745,11 +745,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>持续：同房间所有友方怪物牌点数加1。&lt;br&gt;
-死亡时：移动到一个有友方怪物牌的相邻房间并免死。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>枪手</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -788,16 +783,21 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>回合结束时：召集主牌堆第1张同名牌到与本牌相邻的房间。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>开战前：召集所有相邻房间的所有“史莱姆”牌。&lt;br&gt;
-回合结束时：召集相邻房间的1张“史莱姆”牌。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>回合结束时：召集主牌堆第1张同名牌到与本牌相邻的房间。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>死亡时：召集1张同名牌到相邻房间。</t>
+回合结束时：召集1个相邻房间的1张“史莱姆”牌。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>持续：同房间所有友方怪物牌点数加1。&lt;br&gt;
+死亡时：移动到1个有友方怪物牌的相邻房间并免死。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>死亡时：召集1张同名牌到1个相邻房间，该房间必须有友方的牌。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1214,7 +1214,7 @@
         <v>4</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>7</v>
@@ -1286,7 +1286,7 @@
         <v>4</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="F6" s="3" t="s">
         <v>160</v>
@@ -1310,7 +1310,7 @@
         <v>4</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F7" s="3" t="s">
         <v>162</v>
@@ -1502,7 +1502,7 @@
         <v>4</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="F15" s="3" t="s">
         <v>133</v>
@@ -1614,7 +1614,7 @@
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B20" t="s">
         <v>20</v>
@@ -1626,7 +1626,7 @@
         <v>4</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F20" s="3"/>
       <c r="G20" s="2"/>
@@ -1634,7 +1634,7 @@
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B21" t="s">
         <v>92</v>
@@ -1646,7 +1646,7 @@
         <v>4</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="F21" s="3"/>
       <c r="G21" s="2"/>
@@ -1654,7 +1654,7 @@
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B22" t="s">
         <v>20</v>
@@ -1666,7 +1666,7 @@
         <v>4</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F22" s="3"/>
       <c r="G22" s="2"/>
@@ -2011,7 +2011,7 @@
         <v>4</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="F36" s="3" t="s">
         <v>104</v>
